--- a/relatorio_clinica.xlsx
+++ b/relatorio_clinica.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Especialidade" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Convênio" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolução Mensal" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking Médicos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Atendimentos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Por Especialidade" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Por Convênio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Evolução Mensal" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ranking Médicos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Status Atendimentos" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -48,7 +51,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -56,13 +59,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
